--- a/fluxo-integrado/erros.xlsx
+++ b/fluxo-integrado/erros.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F15F3B5C-35FE-4CAA-830D-1ADFB09F6742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D7C130-553D-44F3-A51F-565DF5B84995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{CD11E3A1-F9F3-41D1-BD39-101160BD6322}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD11E3A1-F9F3-41D1-BD39-101160BD6322}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
   <si>
     <t>Cenário</t>
   </si>
@@ -97,13 +97,37 @@
   </si>
   <si>
     <t>A autodeclaração não apareceu na sequência do requerimento para preenchimento. Ela aparece somente para preenchimento no card.</t>
+  </si>
+  <si>
+    <r>
+      <t>Protocolo 3231253751378 e 5624456001438 - Requerimento criado e perícia agendada. O status Sibe foi alterado para Aguardando Perícia. Entretanto, a divergência 168 foi gravada no requerimento Pendência de agendamento de perícia.</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> O erro está na gravação da divergência 168.</t>
+    </r>
+  </si>
+  <si>
+    <t>Andreia</t>
+  </si>
+  <si>
+    <t>Não gerou: DESCRITIVO DA VALIDAÇÃO DE PERÍODOS DE SEGURADO ESPECIAL</t>
+  </si>
+  <si>
+    <t>Ag Reteste</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,8 +149,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -142,6 +179,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -173,7 +216,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -185,6 +228,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,11 +564,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DE9C44-65BF-4F34-A5BA-C6D4C9A5B85F}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="186.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="130.44140625" customWidth="1"/>
     <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -542,100 +587,128 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="8">
+        <v>2</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="4">
         <v>3</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D3" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="1">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="4">
+        <v>6</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="4">
-        <v>6</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="4" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1">
+        <v>7</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="1">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="1" t="s">
+    <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="4">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D7" s="4" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="1">
-        <v>19</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
+        <v>18</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="1">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
         <v>20</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C10" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D10" s="4" t="s">
         <v>8</v>
       </c>
     </row>

--- a/fluxo-integrado/erros.xlsx
+++ b/fluxo-integrado/erros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44D7C130-553D-44F3-A51F-565DF5B84995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EE85B4-1DD6-4866-9E2D-D212410905DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD11E3A1-F9F3-41D1-BD39-101160BD6322}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Cenário</t>
   </si>
@@ -54,9 +54,6 @@
   </si>
   <si>
     <t>Paraâmetro esta indo true para o SIBE em situações de indeferimento total</t>
-  </si>
-  <si>
-    <t>Em correção</t>
   </si>
   <si>
     <t>Carlos</t>
@@ -178,13 +175,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -216,20 +213,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,59 +569,59 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="8">
+      <c r="A2" s="2">
         <v>2</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>21</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="2">
         <v>3</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="1">
-        <v>4</v>
-      </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>21</v>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
@@ -633,27 +629,27 @@
         <v>6</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="4">
+        <v>7</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="1">
+      <c r="D6" s="4" t="s">
         <v>7</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -661,13 +657,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
@@ -675,27 +671,27 @@
         <v>18</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="1">
+      <c r="A9" s="4">
         <v>19</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>8</v>
+      <c r="D9" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -703,13 +699,13 @@
         <v>20</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/fluxo-integrado/erros.xlsx
+++ b/fluxo-integrado/erros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07EE85B4-1DD6-4866-9E2D-D212410905DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6794A722-580A-4D56-AF7E-8ED7817FC94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD11E3A1-F9F3-41D1-BD39-101160BD6322}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
   <si>
     <t>Cenário</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Ag Reteste</t>
+  </si>
+  <si>
+    <t>Alteração do decurso de prazo OK</t>
   </si>
 </sst>
 </file>
@@ -160,7 +163,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -182,6 +185,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,7 +222,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -226,6 +235,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -560,7 +573,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3DE9C44-65BF-4F34-A5BA-C6D4C9A5B85F}">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.21875" bestFit="1" customWidth="1"/>
@@ -667,28 +680,28 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="4">
+      <c r="A8" s="8">
+        <v>10</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>7</v>
+      <c r="C8" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>17</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>7</v>
@@ -696,15 +709,29 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="4" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>7</v>
       </c>
     </row>

--- a/fluxo-integrado/erros.xlsx
+++ b/fluxo-integrado/erros.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiago.delima\painel_hml_caf\fluxo-integrado\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6794A722-580A-4D56-AF7E-8ED7817FC94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2995A1-60CF-462B-8A0E-066C5E10B51F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD11E3A1-F9F3-41D1-BD39-101160BD6322}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="21">
   <si>
     <t>Cenário</t>
   </si>
@@ -63,9 +63,6 @@
 &lt;!DOCTYPE HTML PUBLIC "-//IETF//DTD HTML 2.0//EN"&gt; &lt;html&gt;&lt;head&gt; &lt;title&gt;502 Proxy Error&lt;/title&gt; &lt;/head&gt;&lt;body&gt; &lt;h1&gt;Proxy Error&lt;/h1&gt; &lt;p&gt;The proxy server received an invalid response from an upstream server.&lt;br /&gt; The proxy server could not handle the request&lt;p&gt;Reason: &lt;strong&gt;Error reading from remote server&lt;/strong&gt;&lt;/p&gt;&lt;/p&gt; &lt;/body&gt;&lt;/html&gt;
 Ocorrência de integração:
 500 : "{"erros":[{"codigo":"SERVICO_PARCEIRO_FALHOU_RESPONDER_SOLICITACAO_DISPSE","mensagem":"Servico parceiro EXTRATO_CNIS falhou ao responder solicitacao do FPSE","parametros":{"tipoErro":"SERVICO_PARCEIRO_FALHOU_RESPONDER_SOLICITACAO_DISPSE","statusCode":422,"content":"</t>
-  </si>
-  <si>
-    <t>Ag Análise</t>
   </si>
   <si>
     <t>Integrou com o Sibe mesmo em exigência de documentação médica (Falar com o Carlos pra tentar replicar e entender esse cenário)</t>
@@ -117,10 +114,10 @@
     <t>Não gerou: DESCRITIVO DA VALIDAÇÃO DE PERÍODOS DE SEGURADO ESPECIAL</t>
   </si>
   <si>
-    <t>Ag Reteste</t>
-  </si>
-  <si>
     <t>Alteração do decurso de prazo OK</t>
+  </si>
+  <si>
+    <t>Corrigido</t>
   </si>
 </sst>
 </file>
@@ -163,7 +160,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -178,19 +175,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -222,21 +213,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -596,44 +583,44 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+      <c r="A2" s="4">
         <v>2</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
+      <c r="A3" s="4">
         <v>3</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="4">
         <v>4</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>20</v>
       </c>
     </row>
@@ -645,10 +632,10 @@
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
@@ -656,13 +643,13 @@
         <v>7</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
@@ -670,41 +657,41 @@
         <v>8</v>
       </c>
       <c r="B7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="2">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="8">
-        <v>10</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4">
-        <v>18</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
@@ -712,13 +699,13 @@
         <v>19</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="D10" s="4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
@@ -726,13 +713,13 @@
         <v>20</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="7" t="s">
-        <v>16</v>
-      </c>
       <c r="D11" s="4" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
